--- a/CSCO.xlsx
+++ b/CSCO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AE9D8C-E179-4E55-8E3A-4C4B829851C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517B30FE-2D68-4D8B-8E92-5FB39826DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25140" yWindow="0" windowWidth="26460" windowHeight="20880" xr2:uid="{5ED8D86A-A1D6-40BE-A8D1-3AD681AED52B}"/>
+    <workbookView xWindow="18040" yWindow="7930" windowWidth="19890" windowHeight="10280" activeTab="1" xr2:uid="{5ED8D86A-A1D6-40BE-A8D1-3AD681AED52B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Main</t>
   </si>
@@ -67,6 +67,60 @@
   </si>
   <si>
     <t>EV</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>FQ426</t>
+  </si>
+  <si>
+    <t>FQ425</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Collaboration</t>
+  </si>
+  <si>
+    <t>Observability</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>FQ326</t>
+  </si>
+  <si>
+    <t>FQ325</t>
+  </si>
+  <si>
+    <t>FQ226</t>
+  </si>
+  <si>
+    <t>FQ225</t>
+  </si>
+  <si>
+    <t>FQ126</t>
+  </si>
+  <si>
+    <t>FQ125</t>
+  </si>
+  <si>
+    <t>FQ124</t>
+  </si>
+  <si>
+    <t>FQ224</t>
+  </si>
+  <si>
+    <t>FQ324</t>
+  </si>
+  <si>
+    <t>FQ424</t>
   </si>
 </sst>
 </file>
@@ -120,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -129,6 +183,26 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -195,7 +269,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Model!$C$3:$AC$3</c:f>
+              <c:f>Model!$Q$8:$AQ$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -285,7 +359,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Model!$C$4:$AC$4</c:f>
+              <c:f>Model!$Q$22:$AQ$22</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="27"/>
@@ -525,6 +599,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -532,7 +607,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1127,15 +1201,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>201719</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>107293</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>38</xdr:col>
       <xdr:colOff>523186</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>118009</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1165,9 +1239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1205,7 +1279,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1311,7 +1385,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1453,7 +1527,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1461,38 +1535,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD7BF36-96F0-4ABA-801F-D66DDEC3058C}">
-  <dimension ref="J2:K7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="J2:L7"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K2" s="6">
+        <v>111.58</v>
+      </c>
+    </row>
+    <row r="3" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K3" s="2">
+        <v>3941.4346650000002</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K4" s="2">
+        <f>+K2*K3</f>
+        <v>439785.27992070001</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K5" s="2">
+        <f>7083+9557</f>
+        <v>16640</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="10:11" x14ac:dyDescent="0.2">
+      <c r="K6" s="2">
+        <f>11932+19371</f>
+        <v>31303</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>9</v>
+      </c>
+      <c r="K7" s="2">
+        <f>+K4-K5+K6</f>
+        <v>454448.27992070001</v>
       </c>
     </row>
   </sheetData>
@@ -1502,567 +1606,1482 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6A1744-E4D5-4196-B3AF-2B9516536BD5}">
-  <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AS30"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="14" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C1" s="11">
+        <v>45225</v>
+      </c>
+      <c r="D1" s="11">
+        <v>45316</v>
+      </c>
+      <c r="E1" s="11">
+        <v>45408</v>
+      </c>
+      <c r="F1" s="11">
+        <v>45499</v>
+      </c>
+      <c r="G1" s="11">
+        <v>45591</v>
+      </c>
+      <c r="H1" s="11">
+        <v>45682</v>
+      </c>
+      <c r="I1" s="11">
+        <v>45773</v>
+      </c>
+      <c r="J1" s="11">
+        <v>45864</v>
+      </c>
+      <c r="K1" s="11">
+        <v>45955</v>
+      </c>
+      <c r="L1" s="11">
+        <v>46046</v>
+      </c>
+      <c r="M1" s="11">
+        <v>46137</v>
+      </c>
+      <c r="N1" s="11">
+        <v>46228</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1">
         <v>35276</v>
       </c>
-      <c r="AA1" s="1"/>
-      <c r="AC1" s="1">
+      <c r="AO1" s="1"/>
+      <c r="AQ1" s="1">
         <v>44772</v>
       </c>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C2">
+      <c r="AR1" s="1"/>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="C2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2">
         <v>1996</v>
       </c>
-      <c r="D2">
+      <c r="R2">
         <v>1997</v>
       </c>
-      <c r="E2">
+      <c r="S2">
         <v>1998</v>
       </c>
-      <c r="F2">
+      <c r="T2">
         <v>1999</v>
       </c>
-      <c r="G2">
-        <f>+F2+1</f>
+      <c r="U2">
+        <f>+T2+1</f>
         <v>2000</v>
       </c>
-      <c r="H2">
-        <f t="shared" ref="H2:AE2" si="0">+G2+1</f>
+      <c r="V2">
+        <f t="shared" ref="V2:AS2" si="0">+U2+1</f>
         <v>2001</v>
       </c>
-      <c r="I2">
+      <c r="W2">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="J2">
+      <c r="X2">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="K2">
+      <c r="Y2">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="L2">
+      <c r="Z2">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="M2">
+      <c r="AA2">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="N2">
+      <c r="AB2">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="O2">
+      <c r="AC2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="P2">
+      <c r="AD2">
         <f t="shared" si="0"/>
         <v>2009</v>
       </c>
-      <c r="Q2">
+      <c r="AE2">
         <f t="shared" si="0"/>
         <v>2010</v>
       </c>
-      <c r="R2">
+      <c r="AF2">
         <f t="shared" si="0"/>
         <v>2011</v>
       </c>
-      <c r="S2">
+      <c r="AG2">
         <f t="shared" si="0"/>
         <v>2012</v>
       </c>
-      <c r="T2">
+      <c r="AH2">
         <f t="shared" si="0"/>
         <v>2013</v>
       </c>
-      <c r="U2">
+      <c r="AI2">
         <f t="shared" si="0"/>
         <v>2014</v>
       </c>
-      <c r="V2">
+      <c r="AJ2">
         <f t="shared" si="0"/>
         <v>2015</v>
       </c>
-      <c r="W2">
+      <c r="AK2">
         <f t="shared" si="0"/>
         <v>2016</v>
       </c>
-      <c r="X2">
+      <c r="AL2">
         <f t="shared" si="0"/>
         <v>2017</v>
       </c>
-      <c r="Y2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="Z2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="AA2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="AB2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="AC2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AD2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AE2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+    <row r="3" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="15">
+        <v>8822</v>
+      </c>
+      <c r="D3" s="15">
+        <v>7081</v>
+      </c>
+      <c r="E3" s="15">
+        <v>6522</v>
+      </c>
+      <c r="F3" s="15">
+        <v>6804</v>
+      </c>
+      <c r="G3" s="15">
+        <v>6753</v>
+      </c>
+      <c r="H3" s="15">
+        <v>6850</v>
+      </c>
+      <c r="I3" s="15">
+        <v>7068</v>
+      </c>
+      <c r="J3" s="15">
+        <v>7633</v>
+      </c>
+      <c r="K3" s="15">
+        <v>7768</v>
+      </c>
+      <c r="L3" s="15">
+        <v>8294</v>
+      </c>
+      <c r="M3" s="15">
+        <v>8815</v>
+      </c>
+      <c r="N3" s="15">
+        <v>9791</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1010</v>
+      </c>
+      <c r="D4" s="15">
+        <v>973</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1304</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1787</v>
+      </c>
+      <c r="G4" s="15">
+        <v>2017</v>
+      </c>
+      <c r="H4" s="15">
+        <v>2111</v>
+      </c>
+      <c r="I4" s="15">
+        <v>2013</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1952</v>
+      </c>
+      <c r="K4" s="15">
+        <v>1980</v>
+      </c>
+      <c r="L4" s="15">
+        <v>2018</v>
+      </c>
+      <c r="M4" s="15">
+        <v>2008</v>
+      </c>
+      <c r="N4" s="15">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1117</v>
+      </c>
+      <c r="D5" s="15">
+        <v>989</v>
+      </c>
+      <c r="E5" s="15">
+        <v>987</v>
+      </c>
+      <c r="F5" s="15">
+        <v>1019</v>
+      </c>
+      <c r="G5" s="15">
+        <v>1085</v>
+      </c>
+      <c r="H5" s="15">
+        <v>996</v>
+      </c>
+      <c r="I5" s="15">
+        <v>1031</v>
+      </c>
+      <c r="J5" s="15">
+        <v>1042</v>
+      </c>
+      <c r="K5" s="15">
+        <v>1055</v>
+      </c>
+      <c r="L5" s="15">
+        <v>1054</v>
+      </c>
+      <c r="M5" s="15">
+        <v>1024</v>
+      </c>
+      <c r="N5" s="15">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="15">
+        <v>190</v>
+      </c>
+      <c r="D6" s="15">
+        <v>188</v>
+      </c>
+      <c r="E6" s="15">
+        <v>211</v>
+      </c>
+      <c r="F6" s="15">
+        <v>248</v>
+      </c>
+      <c r="G6" s="15">
+        <v>258</v>
+      </c>
+      <c r="H6" s="15">
+        <v>277</v>
+      </c>
+      <c r="I6" s="15">
+        <v>261</v>
+      </c>
+      <c r="J6" s="15">
+        <v>259</v>
+      </c>
+      <c r="K6" s="15">
+        <v>274</v>
+      </c>
+      <c r="L6" s="15">
+        <v>277</v>
+      </c>
+      <c r="M6" s="15">
+        <v>269</v>
+      </c>
+      <c r="N6" s="15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15">
+        <v>3529</v>
+      </c>
+      <c r="D7" s="15">
+        <v>3559</v>
+      </c>
+      <c r="E7" s="15">
+        <v>3678</v>
+      </c>
+      <c r="F7" s="15">
+        <v>3784</v>
+      </c>
+      <c r="G7" s="15">
+        <v>3727</v>
+      </c>
+      <c r="H7" s="15">
+        <v>3757</v>
+      </c>
+      <c r="I7" s="15">
+        <v>3775</v>
+      </c>
+      <c r="J7" s="15">
+        <v>3787</v>
+      </c>
+      <c r="K7" s="15">
+        <v>3806</v>
+      </c>
+      <c r="L7" s="15">
+        <v>3707</v>
+      </c>
+      <c r="M7" s="15">
+        <v>3724</v>
+      </c>
+      <c r="N7" s="15">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C8" s="12">
+        <f t="shared" ref="C8" si="1">SUM(C3:C7)</f>
+        <v>14668</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" ref="D8" si="2">SUM(D3:D7)</f>
+        <v>12790</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="3">SUM(E3:E7)</f>
+        <v>12702</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" ref="F8" si="4">SUM(F3:F7)</f>
+        <v>13642</v>
+      </c>
+      <c r="G8" s="12">
+        <f t="shared" ref="G8:M8" si="5">SUM(G3:G7)</f>
+        <v>13840</v>
+      </c>
+      <c r="H8" s="12">
+        <f t="shared" si="5"/>
+        <v>13991</v>
+      </c>
+      <c r="I8" s="12">
+        <f t="shared" si="5"/>
+        <v>14148</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="5"/>
+        <v>14673</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" si="5"/>
+        <v>14883</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" si="5"/>
+        <v>15350</v>
+      </c>
+      <c r="M8" s="12">
+        <f t="shared" si="5"/>
+        <v>15840</v>
+      </c>
+      <c r="N8" s="12">
+        <f>SUM(N3:N7)</f>
+        <v>17252</v>
+      </c>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10">
         <v>4101</v>
       </c>
-      <c r="D3" s="2">
+      <c r="R8" s="10">
         <v>6452</v>
       </c>
-      <c r="E3" s="2">
+      <c r="S8" s="10">
         <v>8489</v>
       </c>
-      <c r="F3" s="2">
+      <c r="T8" s="10">
         <v>12173</v>
       </c>
-      <c r="G3" s="2">
+      <c r="U8" s="10">
         <v>18928</v>
       </c>
-      <c r="H3" s="2">
+      <c r="V8" s="10">
         <v>22293</v>
       </c>
-      <c r="I3" s="2">
+      <c r="W8" s="10">
         <v>18915</v>
       </c>
-      <c r="J3" s="2">
+      <c r="X8" s="10">
         <v>18878</v>
       </c>
-      <c r="K3" s="2">
+      <c r="Y8" s="10">
         <v>22045</v>
       </c>
-      <c r="L3" s="2">
+      <c r="Z8" s="10">
         <v>24801</v>
       </c>
-      <c r="M3" s="2">
+      <c r="AA8" s="10">
         <v>28484</v>
       </c>
-      <c r="N3" s="2">
+      <c r="AB8" s="10">
         <v>34922</v>
       </c>
-      <c r="O3" s="2">
+      <c r="AC8" s="10">
         <v>39540</v>
       </c>
-      <c r="P3" s="2">
+      <c r="AD8" s="10">
         <v>36117</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="AE8" s="10">
         <v>40040</v>
       </c>
-      <c r="R3" s="2">
+      <c r="AF8" s="10">
         <v>43218</v>
       </c>
-      <c r="S3" s="2">
+      <c r="AG8" s="10">
         <v>46061</v>
       </c>
-      <c r="T3" s="2">
+      <c r="AH8" s="10">
         <v>48607</v>
       </c>
-      <c r="U3" s="2">
+      <c r="AI8" s="10">
         <v>47142</v>
       </c>
-      <c r="V3" s="2">
+      <c r="AJ8" s="10">
         <v>49161</v>
       </c>
-      <c r="W3" s="2">
+      <c r="AK8" s="10">
         <v>49247</v>
       </c>
-      <c r="X3" s="2">
+      <c r="AL8" s="10">
         <v>48005</v>
       </c>
-      <c r="Y3" s="2">
+      <c r="AM8" s="10">
         <v>49330</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="AN8" s="10">
         <v>51904</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AO8" s="10">
         <v>49301</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AP8" s="10">
         <v>49818</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="AQ8" s="10">
         <v>51557</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="6" t="s">
+    <row r="9" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="10"/>
+      <c r="AG9" s="10"/>
+      <c r="AH9" s="10"/>
+      <c r="AI9" s="10"/>
+      <c r="AJ9" s="10"/>
+      <c r="AK9" s="10"/>
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="10"/>
+      <c r="AO9" s="10"/>
+      <c r="AP9" s="10"/>
+      <c r="AQ9" s="10"/>
+    </row>
+    <row r="10" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
+      <c r="AL10" s="10"/>
+      <c r="AM10" s="10"/>
+      <c r="AN10" s="10"/>
+      <c r="AO10" s="10"/>
+      <c r="AP10" s="10"/>
+      <c r="AQ10" s="10"/>
+    </row>
+    <row r="11" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
+      <c r="AJ11" s="10"/>
+      <c r="AK11" s="10"/>
+      <c r="AL11" s="10"/>
+      <c r="AM11" s="10"/>
+      <c r="AN11" s="10"/>
+      <c r="AO11" s="10"/>
+      <c r="AP11" s="10"/>
+      <c r="AQ11" s="10"/>
+    </row>
+    <row r="12" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
+      <c r="AL12" s="10"/>
+      <c r="AM12" s="10"/>
+      <c r="AN12" s="10"/>
+      <c r="AO12" s="10"/>
+      <c r="AP12" s="10"/>
+      <c r="AQ12" s="10"/>
+    </row>
+    <row r="13" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+      <c r="AN13" s="10"/>
+      <c r="AO13" s="10"/>
+      <c r="AP13" s="10"/>
+      <c r="AQ13" s="10"/>
+    </row>
+    <row r="14" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
+      <c r="AL14" s="10"/>
+      <c r="AM14" s="10"/>
+      <c r="AN14" s="10"/>
+      <c r="AO14" s="10"/>
+      <c r="AP14" s="10"/>
+      <c r="AQ14" s="10"/>
+    </row>
+    <row r="15" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="10"/>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
+      <c r="AL15" s="10"/>
+      <c r="AM15" s="10"/>
+      <c r="AN15" s="10"/>
+      <c r="AO15" s="10"/>
+      <c r="AP15" s="10"/>
+      <c r="AQ15" s="10"/>
+    </row>
+    <row r="16" spans="1:45" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
+      <c r="AL16" s="10"/>
+      <c r="AM16" s="10"/>
+      <c r="AN16" s="10"/>
+      <c r="AO16" s="10"/>
+      <c r="AP16" s="10"/>
+      <c r="AQ16" s="10"/>
+    </row>
+    <row r="17" spans="2:43" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
+      <c r="AH17" s="10"/>
+      <c r="AI17" s="10"/>
+      <c r="AJ17" s="10"/>
+      <c r="AK17" s="10"/>
+      <c r="AL17" s="10"/>
+      <c r="AM17" s="10"/>
+      <c r="AN17" s="10"/>
+      <c r="AO17" s="10"/>
+      <c r="AP17" s="10"/>
+      <c r="AQ17" s="10"/>
+    </row>
+    <row r="18" spans="2:43" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="10"/>
+      <c r="AQ18" s="10"/>
+    </row>
+    <row r="19" spans="2:43" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+      <c r="AH19" s="10"/>
+      <c r="AI19" s="10"/>
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="10"/>
+      <c r="AL19" s="10"/>
+      <c r="AM19" s="10"/>
+      <c r="AN19" s="10"/>
+      <c r="AO19" s="10"/>
+      <c r="AP19" s="10"/>
+      <c r="AQ19" s="10"/>
+    </row>
+    <row r="20" spans="2:43" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
+      <c r="AL20" s="10"/>
+      <c r="AM20" s="10"/>
+      <c r="AN20" s="10"/>
+      <c r="AO20" s="10"/>
+      <c r="AP20" s="10"/>
+      <c r="AQ20" s="10"/>
+    </row>
+    <row r="21" spans="2:43" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="10"/>
+      <c r="AK21" s="10"/>
+      <c r="AL21" s="10"/>
+      <c r="AM21" s="10"/>
+      <c r="AN21" s="10"/>
+      <c r="AO21" s="10"/>
+      <c r="AP21" s="10"/>
+      <c r="AQ21" s="10"/>
+    </row>
+    <row r="22" spans="2:43" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="Q22" s="6">
         <v>4.05</v>
       </c>
-      <c r="D4" s="6">
+      <c r="R22" s="6">
         <v>6.23</v>
       </c>
-      <c r="E4" s="6">
+      <c r="S22" s="6">
         <v>11.24</v>
       </c>
-      <c r="F4" s="6">
+      <c r="T22" s="6">
         <v>21.88</v>
       </c>
-      <c r="G4" s="6">
+      <c r="U22" s="6">
         <v>46.1</v>
       </c>
-      <c r="H4" s="6">
+      <c r="V22" s="6">
         <v>13.54</v>
       </c>
-      <c r="I4" s="6">
+      <c r="W22" s="6">
         <v>9.2899999999999991</v>
       </c>
-      <c r="J4" s="6">
+      <c r="X22" s="6">
         <v>13.73</v>
       </c>
-      <c r="K4" s="6">
+      <c r="Y22" s="6">
         <v>14.74</v>
       </c>
-      <c r="L4" s="6">
+      <c r="Z22" s="6">
         <v>13.49</v>
       </c>
-      <c r="M4" s="6">
+      <c r="AA22" s="6">
         <v>12.6</v>
       </c>
-      <c r="N4" s="6">
+      <c r="AB22" s="6">
         <v>20.37</v>
       </c>
-      <c r="O4" s="6">
+      <c r="AC22" s="6">
         <v>15.49</v>
       </c>
-      <c r="P4" s="6">
+      <c r="AD22" s="6">
         <v>15.51</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="AE22" s="6">
         <v>16.25</v>
       </c>
-      <c r="R4" s="6">
+      <c r="AF22" s="6">
         <v>11.33</v>
       </c>
-      <c r="S4" s="6">
+      <c r="AG22" s="6">
         <v>11.5</v>
       </c>
-      <c r="T4" s="6">
+      <c r="AH22" s="6">
         <v>19.010000000000002</v>
       </c>
-      <c r="U4" s="6">
+      <c r="AI22" s="6">
         <v>19.329999999999998</v>
       </c>
-      <c r="V4" s="6">
+      <c r="AJ22" s="6">
         <v>22.43</v>
       </c>
-      <c r="W4" s="6">
+      <c r="AK22" s="6">
         <v>24.93</v>
       </c>
-      <c r="X4" s="6">
+      <c r="AL22" s="6">
         <v>26.59</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="AM22" s="6">
         <v>36.909999999999997</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="AN22" s="6">
         <v>49.67</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AO22" s="6">
         <v>43.61</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AP22" s="6">
         <v>52.9</v>
       </c>
-      <c r="AC4" s="6">
+      <c r="AQ22" s="6">
         <v>44.6</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C6" s="7">
-        <f>RATE(2023-1996,0,-C4,AC4)</f>
+    <row r="23" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AQ23" s="6"/>
+    </row>
+    <row r="24" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7">
+        <f>RATE(2023-1996,0,-Q22,AQ22)</f>
         <v>9.2919417686090272E-2</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="T24" s="3"/>
+    </row>
+    <row r="27" spans="2:43" ht="13" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="4">
-        <f>+D3/C3-1</f>
+      <c r="R27" s="4">
+        <f>+R8/Q8-1</f>
         <v>0.57327481102170208</v>
       </c>
-      <c r="E9" s="4">
-        <f t="shared" ref="E9:AC9" si="1">+E3/D3-1</f>
+      <c r="S27" s="4">
+        <f t="shared" ref="S27:AQ27" si="6">+S8/R8-1</f>
         <v>0.31571605703657779</v>
       </c>
-      <c r="F9" s="4">
-        <f t="shared" si="1"/>
+      <c r="T27" s="4">
+        <f t="shared" si="6"/>
         <v>0.43397337731181529</v>
       </c>
-      <c r="G9" s="4">
-        <f>+G3/F3-1</f>
+      <c r="U27" s="4">
+        <f>+U8/T8-1</f>
         <v>0.55491661874640608</v>
       </c>
-      <c r="H9" s="4">
-        <f t="shared" si="1"/>
+      <c r="V27" s="4">
+        <f t="shared" si="6"/>
         <v>0.17777895181741332</v>
       </c>
-      <c r="I9" s="3">
-        <f t="shared" si="1"/>
+      <c r="W27" s="3">
+        <f t="shared" si="6"/>
         <v>-0.15152738527788989</v>
       </c>
-      <c r="J9" s="3">
-        <f t="shared" si="1"/>
+      <c r="X27" s="3">
+        <f t="shared" si="6"/>
         <v>-1.9561194818926708E-3</v>
       </c>
-      <c r="K9" s="4">
-        <f t="shared" si="1"/>
+      <c r="Y27" s="4">
+        <f t="shared" si="6"/>
         <v>0.16776141540417422</v>
       </c>
-      <c r="L9" s="4">
-        <f t="shared" si="1"/>
+      <c r="Z27" s="4">
+        <f t="shared" si="6"/>
         <v>0.12501701066001369</v>
       </c>
-      <c r="M9" s="4">
-        <f t="shared" si="1"/>
+      <c r="AA27" s="4">
+        <f t="shared" si="6"/>
         <v>0.14850207652917224</v>
       </c>
-      <c r="N9" s="4">
-        <f t="shared" si="1"/>
+      <c r="AB27" s="4">
+        <f t="shared" si="6"/>
         <v>0.22602162617609878</v>
       </c>
-      <c r="O9" s="4">
-        <f t="shared" si="1"/>
+      <c r="AC27" s="4">
+        <f t="shared" si="6"/>
         <v>0.13223755798636971</v>
       </c>
-      <c r="P9" s="3">
-        <f t="shared" si="1"/>
+      <c r="AD27" s="3">
+        <f t="shared" si="6"/>
         <v>-8.6570561456752682E-2</v>
       </c>
-      <c r="Q9" s="3">
-        <f t="shared" si="1"/>
+      <c r="AE27" s="3">
+        <f t="shared" si="6"/>
         <v>0.10861920979040351</v>
       </c>
-      <c r="R9" s="3">
-        <f t="shared" si="1"/>
+      <c r="AF27" s="3">
+        <f t="shared" si="6"/>
         <v>7.9370629370629331E-2</v>
       </c>
-      <c r="S9" s="3">
-        <f t="shared" si="1"/>
+      <c r="AG27" s="3">
+        <f t="shared" si="6"/>
         <v>6.5782775695312212E-2</v>
       </c>
-      <c r="T9" s="3">
-        <f t="shared" si="1"/>
+      <c r="AH27" s="3">
+        <f t="shared" si="6"/>
         <v>5.5274527257332728E-2</v>
       </c>
-      <c r="U9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AI27" s="5">
+        <f t="shared" si="6"/>
         <v>-3.0139691813936276E-2</v>
       </c>
-      <c r="V9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AJ27" s="5">
+        <f t="shared" si="6"/>
         <v>4.2828051419116608E-2</v>
       </c>
-      <c r="W9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AK27" s="5">
+        <f t="shared" si="6"/>
         <v>1.749354162852601E-3</v>
       </c>
-      <c r="X9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AL27" s="5">
+        <f t="shared" si="6"/>
         <v>-2.5219810343777294E-2</v>
       </c>
-      <c r="Y9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AM27" s="5">
+        <f t="shared" si="6"/>
         <v>2.7601291532131977E-2</v>
       </c>
-      <c r="Z9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AN27" s="5">
+        <f t="shared" si="6"/>
         <v>5.2179201297384958E-2</v>
       </c>
-      <c r="AA9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AO27" s="5">
+        <f t="shared" si="6"/>
         <v>-5.0150277435265123E-2</v>
       </c>
-      <c r="AB9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AP27" s="5">
+        <f t="shared" si="6"/>
         <v>1.0486602705827464E-2</v>
       </c>
-      <c r="AC9" s="5">
-        <f t="shared" si="1"/>
+      <c r="AQ27" s="5">
+        <f t="shared" si="6"/>
         <v>3.490706170460478E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+    <row r="28" spans="2:43" ht="13" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="3">
-        <f t="shared" ref="D10:AC10" si="2">+D4/C4-1</f>
+      <c r="R28" s="3">
+        <f t="shared" ref="R28:AQ28" si="7">+R22/Q22-1</f>
         <v>0.53827160493827186</v>
       </c>
-      <c r="E10" s="3">
-        <f t="shared" si="2"/>
+      <c r="S28" s="3">
+        <f t="shared" si="7"/>
         <v>0.80417335473515239</v>
       </c>
-      <c r="F10" s="3">
-        <f t="shared" si="2"/>
+      <c r="T28" s="3">
+        <f t="shared" si="7"/>
         <v>0.94661921708185037</v>
       </c>
-      <c r="G10" s="3">
-        <f t="shared" si="2"/>
+      <c r="U28" s="3">
+        <f t="shared" si="7"/>
         <v>1.1069469835466181</v>
       </c>
-      <c r="H10" s="4">
-        <f t="shared" si="2"/>
+      <c r="V28" s="4">
+        <f t="shared" si="7"/>
         <v>-0.70629067245119304</v>
       </c>
-      <c r="I10" s="3">
-        <f t="shared" si="2"/>
+      <c r="W28" s="3">
+        <f t="shared" si="7"/>
         <v>-0.31388478581979318</v>
       </c>
-      <c r="J10" s="3">
-        <f t="shared" si="2"/>
+      <c r="X28" s="3">
+        <f t="shared" si="7"/>
         <v>0.47793326157158256</v>
       </c>
-      <c r="K10" s="4">
-        <f t="shared" si="2"/>
+      <c r="Y28" s="4">
+        <f t="shared" si="7"/>
         <v>7.3561544064093098E-2</v>
       </c>
-      <c r="L10" s="4">
-        <f t="shared" si="2"/>
+      <c r="Z28" s="4">
+        <f t="shared" si="7"/>
         <v>-8.4803256445047492E-2</v>
       </c>
-      <c r="M10" s="4">
-        <f t="shared" si="2"/>
+      <c r="AA28" s="4">
+        <f t="shared" si="7"/>
         <v>-6.5974796145292891E-2</v>
       </c>
-      <c r="N10" s="4">
-        <f t="shared" si="2"/>
+      <c r="AB28" s="4">
+        <f t="shared" si="7"/>
         <v>0.6166666666666667</v>
       </c>
-      <c r="O10" s="4">
-        <f t="shared" si="2"/>
+      <c r="AC28" s="4">
+        <f t="shared" si="7"/>
         <v>-0.23956799214531177</v>
       </c>
-      <c r="P10" s="3">
-        <f t="shared" si="2"/>
+      <c r="AD28" s="3">
+        <f t="shared" si="7"/>
         <v>1.2911555842478606E-3</v>
       </c>
-      <c r="Q10" s="3">
-        <f t="shared" si="2"/>
+      <c r="AE28" s="3">
+        <f t="shared" si="7"/>
         <v>4.7711154094132846E-2</v>
       </c>
-      <c r="R10" s="3">
-        <f t="shared" si="2"/>
+      <c r="AF28" s="3">
+        <f t="shared" si="7"/>
         <v>-0.30276923076923079</v>
       </c>
-      <c r="S10" s="3">
-        <f t="shared" si="2"/>
+      <c r="AG28" s="3">
+        <f t="shared" si="7"/>
         <v>1.5004413062665423E-2</v>
       </c>
-      <c r="T10" s="3">
-        <f t="shared" si="2"/>
+      <c r="AH28" s="3">
+        <f t="shared" si="7"/>
         <v>0.65304347826086961</v>
       </c>
-      <c r="U10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AI28" s="5">
+        <f t="shared" si="7"/>
         <v>1.6833245660178742E-2</v>
       </c>
-      <c r="V10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AJ28" s="5">
+        <f t="shared" si="7"/>
         <v>0.16037247801345078</v>
       </c>
-      <c r="W10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AK28" s="5">
+        <f t="shared" si="7"/>
         <v>0.1114578689255461</v>
       </c>
-      <c r="X10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AL28" s="5">
+        <f t="shared" si="7"/>
         <v>6.6586442037705584E-2</v>
       </c>
-      <c r="Y10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AM28" s="5">
+        <f t="shared" si="7"/>
         <v>0.38811583301993213</v>
       </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AN28" s="5">
+        <f t="shared" si="7"/>
         <v>0.34570577079382292</v>
       </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AO28" s="5">
+        <f t="shared" si="7"/>
         <v>-0.12200523454801693</v>
       </c>
-      <c r="AB10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AP28" s="5">
+        <f t="shared" si="7"/>
         <v>0.21302453565695934</v>
       </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="2"/>
+      <c r="AQ28" s="5">
+        <f t="shared" si="7"/>
         <v>-0.15689981096408312</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="D12" s="6">
-        <f>CORREL(C3:AC3,C4:AC4)</f>
+    <row r="30" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="R30" s="6">
+        <f>CORREL(Q8:AQ8,Q22:AQ22)</f>
         <v>0.55101552180960389</v>
       </c>
     </row>
